--- a/data_repository/repository_overview/repository_overview.xlsx
+++ b/data_repository/repository_overview/repository_overview.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27328"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\caspe\ModelQuestions\data_repository\repository_overview\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://solisservices-my.sharepoint.com/personal/s_scheider_uu_nl/Documents/Documents/GitHub/ModelQuestions/data_repository/repository_overview/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{70866647-2744-47CB-9B10-A6C8077A2CA8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="7" documentId="13_ncr:1_{70866647-2744-47CB-9B10-A6C8077A2CA8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C81CBB1F-9474-49D6-B451-128AAF0294F4}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="2100" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="overview" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="87">
   <si>
     <t>dataset_id</t>
   </si>
@@ -285,6 +285,9 @@
   </si>
   <si>
     <t>data_id</t>
+  </si>
+  <si>
+    <t>Map visualization</t>
   </si>
 </sst>
 </file>
@@ -612,21 +615,21 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:K11"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="10.28515625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="19.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="40.85546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="115.7109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="34.28515625" customWidth="1"/>
-    <col min="6" max="6" width="45.42578125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="54.5703125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="17.28515625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="23.140625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="21.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.26953125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19.453125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="40.81640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="115.7265625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="34.26953125" customWidth="1"/>
+    <col min="6" max="6" width="45.453125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="54.54296875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="17.26953125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="23.1796875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="21.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -661,7 +664,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -693,7 +696,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>5</v>
       </c>
@@ -722,7 +725,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>6</v>
       </c>
@@ -751,7 +754,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>7</v>
       </c>
@@ -780,7 +783,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>8</v>
       </c>
@@ -809,7 +812,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>9</v>
       </c>
@@ -838,7 +841,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>10</v>
       </c>
@@ -870,7 +873,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>11</v>
       </c>
@@ -902,7 +905,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>12</v>
       </c>
@@ -934,7 +937,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>13</v>
       </c>
@@ -946,17 +949,18 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{623857EF-CD61-4325-A591-0467B0C18872}">
-  <dimension ref="A1:F6"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:G6"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
-    <col min="2" max="2" width="23.5703125" customWidth="1"/>
-    <col min="3" max="3" width="17.7109375" customWidth="1"/>
-    <col min="4" max="4" width="24.7109375" customWidth="1"/>
-    <col min="5" max="5" width="30.85546875" customWidth="1"/>
+    <col min="2" max="2" width="23.54296875" customWidth="1"/>
+    <col min="3" max="3" width="109.6328125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="35.54296875" customWidth="1"/>
+    <col min="5" max="5" width="24.7265625" customWidth="1"/>
+    <col min="6" max="6" width="30.81640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>85</v>
       </c>
@@ -967,16 +971,19 @@
         <v>34</v>
       </c>
       <c r="D1" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -987,16 +994,19 @@
         <v>16</v>
       </c>
       <c r="D2" t="s">
+        <v>43</v>
+      </c>
+      <c r="E2" t="s">
         <v>42</v>
       </c>
-      <c r="E2" t="s">
+      <c r="F2" t="s">
         <v>17</v>
       </c>
-      <c r="F2" t="s">
+      <c r="G2" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>5</v>
       </c>
@@ -1006,17 +1016,17 @@
       <c r="C3" t="s">
         <v>19</v>
       </c>
-      <c r="D3" t="s">
+      <c r="E3" t="s">
         <v>45</v>
       </c>
-      <c r="E3" t="s">
+      <c r="F3" t="s">
         <v>20</v>
       </c>
-      <c r="F3" t="s">
+      <c r="G3" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>6</v>
       </c>
@@ -1027,16 +1037,19 @@
         <v>22</v>
       </c>
       <c r="D4" t="s">
+        <v>53</v>
+      </c>
+      <c r="E4" t="s">
         <v>54</v>
       </c>
-      <c r="E4" t="s">
+      <c r="F4" t="s">
         <v>26</v>
       </c>
-      <c r="F4" t="s">
+      <c r="G4" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>7</v>
       </c>
@@ -1046,17 +1059,17 @@
       <c r="C5" t="s">
         <v>24</v>
       </c>
-      <c r="D5" t="s">
+      <c r="E5" t="s">
         <v>46</v>
       </c>
-      <c r="E5" t="s">
+      <c r="F5" t="s">
         <v>25</v>
       </c>
-      <c r="F5" t="s">
+      <c r="G5" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>11</v>
       </c>
@@ -1066,13 +1079,13 @@
       <c r="C6" t="s">
         <v>62</v>
       </c>
-      <c r="D6" t="s">
+      <c r="E6" t="s">
         <v>63</v>
       </c>
-      <c r="E6" t="s">
+      <c r="F6" t="s">
         <v>64</v>
       </c>
-      <c r="F6" t="s">
+      <c r="G6" t="s">
         <v>68</v>
       </c>
     </row>
@@ -1084,15 +1097,15 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AF2A09FD-3BF0-4A4B-AECF-01B13C4A05BC}">
   <dimension ref="A1:D11"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="10.28515625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="102.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="166.5703125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="54.28515625" customWidth="1"/>
+    <col min="1" max="1" width="10.26953125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="102.7265625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="166.54296875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="54.26953125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1106,7 +1119,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -1117,7 +1130,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>5</v>
       </c>
@@ -1125,7 +1138,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>6</v>
       </c>
@@ -1136,7 +1149,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>7</v>
       </c>
@@ -1144,17 +1157,17 @@
         <v>77</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>10</v>
       </c>
@@ -1165,7 +1178,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>11</v>
       </c>
@@ -1176,12 +1189,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>13</v>
       </c>

--- a/data_repository/repository_overview/repository_overview.xlsx
+++ b/data_repository/repository_overview/repository_overview.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://solisservices-my.sharepoint.com/personal/s_scheider_uu_nl/Documents/Documents/GitHub/ModelQuestions/data_repository/repository_overview/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="7" documentId="13_ncr:1_{70866647-2744-47CB-9B10-A6C8077A2CA8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C81CBB1F-9474-49D6-B451-128AAF0294F4}"/>
+  <xr:revisionPtr revIDLastSave="8" documentId="13_ncr:1_{70866647-2744-47CB-9B10-A6C8077A2CA8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{36C7A67B-C08C-4436-BCA9-A2C0410919A1}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="overview" sheetId="1" r:id="rId1"/>
@@ -294,7 +294,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -306,6 +306,14 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -328,14 +336,17 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -349,6 +360,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -993,7 +1008,7 @@
       <c r="C2" t="s">
         <v>16</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D2" s="2" t="s">
         <v>43</v>
       </c>
       <c r="E2" t="s">
@@ -1090,6 +1105,9 @@
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="D2" r:id="rId1" xr:uid="{96FDED8E-BA22-4009-9A6B-E7F9067C5F95}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
